--- a/output/pdf_financials_xlsx/RFA.xlsx
+++ b/output/pdf_financials_xlsx/RFA.xlsx
@@ -431,6 +431,19 @@
   </sheetPr>
   <dimension ref="A1:K135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/RFA.xlsx
+++ b/output/pdf_financials_xlsx/RFA.xlsx
@@ -934,22 +934,22 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>2.026</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.442</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.288</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.287</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
@@ -1744,22 +1744,22 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>191.155</v>
+        <v>189.129</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>197.886</v>
+        <v>197.444</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-175.699</v>
+        <v>-175.987</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>116.618</v>
+        <v>116.331</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>234.116</v>
+        <v>233.806</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>159.163</v>
+        <v>159.16</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -1844,16 +1844,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>191.155</v>
+        <v>189.129</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>197.886</v>
+        <v>197.444</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-175.699</v>
+        <v>-175.987</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>116.618</v>
+        <v>116.331</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>78.752</v>
@@ -1894,16 +1894,16 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>41.24893724456107</v>
+        <v>40.81175094622997</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>147.8095892559699</v>
+        <v>147.4794403902031</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-122.975649702883</v>
+        <v>-123.1772273277666</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>79.6690759540368</v>
+        <v>79.47300823894301</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>59.17510125260176</v>
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>42.844</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>48.222</v>
@@ -2055,29 +2055,27 @@
         <v>52.832</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>3.025</v>
+        <v>71.444</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>59.041</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>8.311999999999999</v>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I34" s="3" t="n">
+        <v>0.221474</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>29.168</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>28.94</v>
       </c>
       <c r="L34" s="1" t="inlineStr">
         <is>
@@ -2138,7 +2136,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>42.844</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>48.222</v>
@@ -2147,29 +2145,27 @@
         <v>52.832</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>3.025</v>
+        <v>71.444</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>59.041</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>8.311999999999999</v>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I36" s="3" t="n">
+        <v>0.221474</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>29.168</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>28.94</v>
       </c>
       <c r="L36" s="1" t="inlineStr">
         <is>
@@ -2684,7 +2680,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>182.33</v>
+        <v>139.486</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -2712,10 +2708,10 @@
         </is>
       </c>
       <c r="J48" s="3" t="n">
-        <v>351.099</v>
+        <v>321.931</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>598.453</v>
+        <v>569.513</v>
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
@@ -9961,7 +9957,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -12171,7 +12167,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -15273,7 +15269,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
@@ -24121,7 +24117,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E246" s="5" t="n">
@@ -25916,7 +25912,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -31869,7 +31865,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -56654,7 +56650,7 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
@@ -58072,7 +58068,7 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
@@ -59133,7 +59129,7 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
@@ -59344,7 +59340,7 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
@@ -59766,7 +59762,7 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
@@ -60610,7 +60606,7 @@
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
@@ -61225,7 +61221,7 @@
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
@@ -61298,7 +61294,7 @@
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
@@ -63995,7 +63991,7 @@
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E818" t="inlineStr">
@@ -65340,7 +65336,7 @@
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
@@ -67430,7 +67426,7 @@
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
@@ -69524,7 +69520,7 @@
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E897" t="inlineStr">
@@ -70942,7 +70938,7 @@
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
@@ -73801,7 +73797,7 @@
       </c>
       <c r="D958" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E958" t="inlineStr">
@@ -75769,7 +75765,7 @@
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E986" t="inlineStr">
@@ -76976,7 +76972,7 @@
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
@@ -79772,7 +79768,7 @@
       </c>
       <c r="D1043" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E1043" t="inlineStr">

--- a/output/pdf_financials_xlsx/RFA.xlsx
+++ b/output/pdf_financials_xlsx/RFA.xlsx
@@ -1794,22 +1794,22 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.511</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.575</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.755</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.859</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.249</v>
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
@@ -1844,16 +1844,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>189.129</v>
+        <v>189.64</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>197.444</v>
+        <v>198.019</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-175.987</v>
+        <v>-175.232</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>116.331</v>
+        <v>117.19</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>78.752</v>
@@ -1894,16 +1894,16 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>40.81175094622997</v>
+        <v>40.92201856639146</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>147.4794403902031</v>
+        <v>147.9089326929541</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-123.1772273277666</v>
+        <v>-122.6487859847557</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>79.47300823894301</v>
+        <v>80.05984505868369</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>59.17510125260176</v>
@@ -5066,22 +5066,22 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.511</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.575</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.755</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.859</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.911</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>1.049</v>
       </c>
       <c r="I100" s="1" t="inlineStr">
         <is>
@@ -44438,7 +44438,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E535" t="inlineStr">
         <is>
           <t>-</t>
@@ -50664,7 +50668,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D627" t="inlineStr"/>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E627" t="inlineStr">
         <is>
           <t>-</t>
@@ -60182,7 +60190,11 @@
           <t>Depreciation of property and equipment 249 235</t>
         </is>
       </c>
-      <c r="D763" t="inlineStr"/>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E763" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RFA.xlsx
+++ b/output/pdf_financials_xlsx/RFA.xlsx
@@ -48793,7 +48793,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E600" t="inlineStr">
         <is>
           <t>-</t>
@@ -67716,7 +67720,11 @@
           <t>Income tax recovery (expense) 21</t>
         </is>
       </c>
-      <c r="D871" t="inlineStr"/>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E871" t="inlineStr">
         <is>
           <t>-</t>
